--- a/assets/downloads/CotizacionJIMMY MARCELO HUATUCO.xlsx
+++ b/assets/downloads/CotizacionJIMMY MARCELO HUATUCO.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId4"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="115">
   <si>
     <t>PRO MUNDO COMEX S.A.C.</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>TELEFONO:</t>
-  </si>
-  <si>
-    <t>946 049 931</t>
   </si>
   <si>
     <t>CLIENTE:</t>
@@ -1769,20 +1766,20 @@
       <c r="B11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>17</v>
+      <c r="C11" s="20">
+        <v>51912705923</v>
       </c>
       <c r="D11" s="44"/>
       <c r="E11" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="57" t="s">
         <v>18</v>
-      </c>
-      <c r="F11" s="57" t="s">
-        <v>19</v>
       </c>
       <c r="G11" s="74"/>
       <c r="H11" s="42"/>
       <c r="I11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J11" s="103" t="str">
         <f>'2'!E7</f>
@@ -1806,7 +1803,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="75" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="75"/>
       <c r="D13" s="75"/>
@@ -1817,15 +1814,15 @@
       <c r="I13" s="75"/>
       <c r="J13" s="75"/>
       <c r="K13" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="12" t="s">
         <v>22</v>
-      </c>
-      <c r="L13" s="12" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="76" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="76"/>
       <c r="D14" s="76"/>
@@ -1840,12 +1837,12 @@
         <v>0</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="77" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="77"/>
       <c r="D15" s="77"/>
@@ -1860,12 +1857,12 @@
         <v>0</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16" s="60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="60"/>
       <c r="D16" s="60"/>
@@ -1880,7 +1877,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1911,7 +1908,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="78" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="78"/>
       <c r="D19" s="78"/>
@@ -1921,18 +1918,18 @@
       <c r="H19" s="21"/>
       <c r="I19" s="21"/>
       <c r="J19" s="12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K19" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="12" t="s">
         <v>22</v>
-      </c>
-      <c r="L19" s="12" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C20" s="58"/>
       <c r="D20" s="58"/>
@@ -1950,15 +1947,15 @@
         <v>0</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="58"/>
       <c r="D21" s="58"/>
@@ -1975,12 +1972,12 @@
         <v>0</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="B22" s="57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="57"/>
       <c r="D22" s="57"/>
@@ -1997,12 +1994,12 @@
         <v>0</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="B23" s="60" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="60"/>
       <c r="D23" s="60"/>
@@ -2017,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2035,7 +2032,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="B25" s="57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="57"/>
       <c r="D25" s="57"/>
@@ -2045,19 +2042,19 @@
       <c r="H25" s="57"/>
       <c r="I25" s="57"/>
       <c r="J25" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K25" s="18" t="str">
         <f>'2'!E31</f>
         <v>0</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="B26" s="60" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="60"/>
       <c r="D26" s="60"/>
@@ -2071,7 +2068,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2086,7 +2083,7 @@
     </row>
     <row r="28" spans="1:14" customHeight="1" ht="15.6">
       <c r="B28" s="61" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="61"/>
       <c r="D28" s="61"/>
@@ -2097,15 +2094,15 @@
       <c r="I28" s="61"/>
       <c r="J28" s="61"/>
       <c r="K28" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="32" t="s">
         <v>22</v>
-      </c>
-      <c r="L28" s="32" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="B29" s="58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C29" s="58"/>
       <c r="D29" s="58"/>
@@ -2120,12 +2117,12 @@
         <v>0</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="B30" s="58" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" s="58"/>
       <c r="D30" s="58"/>
@@ -2136,16 +2133,16 @@
       <c r="I30" s="58"/>
       <c r="J30" s="58"/>
       <c r="K30" s="17" t="str">
-        <f>IF('2'!I7&lt;1, '2'!I7*J11, '2'!I7*J11)</f>
+        <f>IF(J11&lt;1, '2'!I7, '2'!I7*J11)</f>
         <v>0</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="B31" s="57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" s="57"/>
       <c r="D31" s="57"/>
@@ -2160,12 +2157,12 @@
         <v>0</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="B32" s="60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="60"/>
       <c r="D32" s="60"/>
@@ -2180,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2198,7 +2195,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="B34" s="68" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" s="69"/>
       <c r="D34" s="69"/>
@@ -2213,28 +2210,28 @@
     </row>
     <row r="35" spans="1:14">
       <c r="B35" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="65" t="s">
         <v>44</v>
-      </c>
-      <c r="C35" s="65" t="s">
-        <v>45</v>
       </c>
       <c r="D35" s="66"/>
       <c r="E35" s="67"/>
       <c r="F35" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" s="65" t="s">
         <v>46</v>
-      </c>
-      <c r="G35" s="65" t="s">
-        <v>47</v>
       </c>
       <c r="H35" s="67"/>
       <c r="I35" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J35" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="K35" s="56" t="s">
         <v>48</v>
-      </c>
-      <c r="J35" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="K35" s="56" t="s">
-        <v>49</v>
       </c>
       <c r="L35" s="56"/>
     </row>
@@ -2243,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -2276,7 +2273,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -2306,7 +2303,7 @@
     </row>
     <row r="38" spans="1:14">
       <c r="B38" s="102" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
@@ -2367,7 +2364,7 @@
     </row>
     <row r="42" spans="1:14" customHeight="1" ht="18">
       <c r="B42" s="33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
@@ -2381,7 +2378,7 @@
     </row>
     <row r="43" spans="1:14" customHeight="1" ht="18">
       <c r="B43" s="73" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" s="73"/>
       <c r="D43" s="73"/>
@@ -2396,7 +2393,7 @@
     </row>
     <row r="44" spans="1:14" customHeight="1" ht="18">
       <c r="B44" s="73" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C44" s="73"/>
       <c r="D44" s="73"/>
@@ -2411,7 +2408,7 @@
     </row>
     <row r="45" spans="1:14" customHeight="1" ht="18">
       <c r="B45" s="73" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C45" s="73"/>
       <c r="D45" s="73"/>
@@ -2426,7 +2423,7 @@
     </row>
     <row r="46" spans="1:14" customHeight="1" ht="18">
       <c r="B46" s="73" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46" s="73"/>
       <c r="D46" s="73"/>
@@ -2441,7 +2438,7 @@
     </row>
     <row r="47" spans="1:14" customHeight="1" ht="18">
       <c r="B47" s="73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47" s="73"/>
       <c r="D47" s="73"/>
@@ -2500,7 +2497,7 @@
       <c r="B51" s="47"/>
       <c r="C51" s="47"/>
       <c r="D51" s="62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E51" s="62"/>
       <c r="F51" s="62"/>
@@ -2518,7 +2515,7 @@
     </row>
     <row r="54" spans="1:14" customHeight="1" ht="21">
       <c r="B54" s="79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C54" s="79"/>
       <c r="D54" s="79"/>
@@ -2533,7 +2530,7 @@
     </row>
     <row r="56" spans="1:14">
       <c r="B56" s="80" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" s="80"/>
       <c r="D56" s="80"/>
@@ -2548,7 +2545,7 @@
     </row>
     <row r="57" spans="1:14">
       <c r="B57" s="80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57" s="80"/>
       <c r="D57" s="80"/>
@@ -2563,7 +2560,7 @@
     </row>
     <row r="58" spans="1:14">
       <c r="B58" s="58" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58" s="58"/>
       <c r="D58" s="58"/>
@@ -2578,7 +2575,7 @@
     </row>
     <row r="59" spans="1:14">
       <c r="B59" s="80" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" s="80"/>
       <c r="D59" s="80"/>
@@ -2593,7 +2590,7 @@
     </row>
     <row r="60" spans="1:14">
       <c r="B60" s="80" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C60" s="80"/>
       <c r="D60" s="80"/>
@@ -2608,7 +2605,7 @@
     </row>
     <row r="61" spans="1:14">
       <c r="B61" s="58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C61" s="58"/>
       <c r="D61" s="58"/>
@@ -2623,7 +2620,7 @@
     </row>
     <row r="62" spans="1:14">
       <c r="B62" s="80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C62" s="80"/>
       <c r="D62" s="80"/>
@@ -2638,7 +2635,7 @@
     </row>
     <row r="63" spans="1:14">
       <c r="B63" s="80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C63" s="80"/>
       <c r="D63" s="80"/>
@@ -2653,7 +2650,7 @@
     </row>
     <row r="64" spans="1:14">
       <c r="B64" s="80" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" s="80"/>
       <c r="D64" s="80"/>
@@ -2668,7 +2665,7 @@
     </row>
     <row r="65" spans="1:14">
       <c r="B65" s="80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C65" s="80"/>
       <c r="D65" s="80"/>
@@ -2683,7 +2680,7 @@
     </row>
     <row r="66" spans="1:14">
       <c r="B66" s="80" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C66" s="80"/>
       <c r="D66" s="80"/>
@@ -2698,7 +2695,7 @@
     </row>
     <row r="67" spans="1:14">
       <c r="B67" s="80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C67" s="80"/>
       <c r="D67" s="80"/>
@@ -2713,7 +2710,7 @@
     </row>
     <row r="68" spans="1:14">
       <c r="B68" s="80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C68" s="80"/>
       <c r="D68" s="80"/>
@@ -2728,7 +2725,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="B69" s="80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C69" s="80"/>
       <c r="D69" s="80"/>
@@ -2743,7 +2740,7 @@
     </row>
     <row r="70" spans="1:14">
       <c r="B70" s="80" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C70" s="80"/>
       <c r="D70" s="80"/>
@@ -2758,7 +2755,7 @@
     </row>
     <row r="71" spans="1:14">
       <c r="B71" s="80" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C71" s="80"/>
       <c r="D71" s="80"/>
@@ -2773,7 +2770,7 @@
     </row>
     <row r="72" spans="1:14">
       <c r="B72" s="80" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C72" s="80"/>
       <c r="D72" s="80"/>
@@ -2788,7 +2785,7 @@
     </row>
     <row r="73" spans="1:14">
       <c r="B73" s="76" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C73" s="76"/>
       <c r="D73" s="76"/>
@@ -2803,7 +2800,7 @@
     </row>
     <row r="74" spans="1:14">
       <c r="B74" s="80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C74" s="80"/>
       <c r="D74" s="80"/>
@@ -2818,7 +2815,7 @@
     </row>
     <row r="75" spans="1:14">
       <c r="B75" s="76" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C75" s="76"/>
       <c r="D75" s="76"/>
@@ -2833,7 +2830,7 @@
     </row>
     <row r="76" spans="1:14">
       <c r="B76" s="80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C76" s="80"/>
       <c r="D76" s="80"/>
@@ -2848,7 +2845,7 @@
     </row>
     <row r="77" spans="1:14">
       <c r="B77" s="80" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C77" s="80"/>
       <c r="D77" s="80"/>
@@ -2863,7 +2860,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="B78" s="80" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C78" s="80"/>
       <c r="D78" s="80"/>
@@ -2878,7 +2875,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="B79" s="80" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C79" s="80"/>
       <c r="D79" s="80"/>
@@ -2893,7 +2890,7 @@
     </row>
     <row r="80" spans="1:14">
       <c r="B80" s="80" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C80" s="80"/>
       <c r="D80" s="80"/>
@@ -2909,7 +2906,7 @@
     <row r="81" spans="1:14">
       <c r="A81" s="41"/>
       <c r="B81" s="81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C81" s="81"/>
       <c r="D81" s="81"/>
@@ -2925,7 +2922,7 @@
     <row r="82" spans="1:14">
       <c r="A82" s="41"/>
       <c r="B82" s="80" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C82" s="80"/>
       <c r="D82" s="80"/>
@@ -2941,7 +2938,7 @@
     <row r="83" spans="1:14">
       <c r="A83" s="41"/>
       <c r="B83" s="81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C83" s="81"/>
       <c r="D83" s="81"/>
@@ -3190,7 +3187,7 @@
   <sheetData>
     <row r="3" spans="1:9">
       <c r="B3" s="84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" s="83"/>
       <c r="D3" s="83"/>
@@ -3200,21 +3197,21 @@
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="87" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="89" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="89" t="s">
         <v>89</v>
-      </c>
-      <c r="C5" s="89" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="89" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="89" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="83" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="83">
         <v>0</v>
@@ -3226,15 +3223,15 @@
         <v>240.3</v>
       </c>
       <c r="H6" s="85" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="85" t="s">
         <v>92</v>
-      </c>
-      <c r="I6" s="85" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="83" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="83">
         <v>0</v>
@@ -3246,7 +3243,7 @@
         <v>1.02</v>
       </c>
       <c r="H7" s="86" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I7" s="86">
         <v>350</v>
@@ -3254,7 +3251,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="83" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8" s="90">
         <v>7.5283251231527</v>
@@ -3266,7 +3263,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C9" s="90">
         <v>0</v>
@@ -3278,7 +3275,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="83" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="83">
         <v>290</v>
@@ -3293,7 +3290,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="B11" s="83" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11" s="90" t="str">
         <f>C8*C10</f>
@@ -3310,7 +3307,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="B12" s="88" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C12" s="90" t="str">
         <f>C10*C9</f>
@@ -3327,7 +3324,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="B13" s="83" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C13" s="93" t="str">
         <f>C11/E11</f>
@@ -3341,7 +3338,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C14" s="90" t="str">
         <f>E14*C13</f>
@@ -3358,7 +3355,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="83" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15" s="90" t="str">
         <f>C11+C14</f>
@@ -3375,7 +3372,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="88" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" s="90" t="str">
         <f>C12+C14</f>
@@ -3392,7 +3389,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="B17" s="83" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" s="90" t="str">
         <f>IF(E15&gt;5000,100*C13,50*C13)</f>
@@ -3409,7 +3406,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="B18" s="83" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C18" s="90" t="str">
         <f>C15+C17</f>
@@ -3426,7 +3423,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" s="88" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C19" s="90" t="str">
         <f>C16+C17</f>
@@ -3443,7 +3440,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="B23" s="84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C23" s="83"/>
       <c r="D23" s="83"/>
@@ -3451,7 +3448,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="B26" s="83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C26" s="90">
         <v>0</v>
@@ -3478,7 +3475,7 @@
     </row>
     <row r="28" spans="1:9">
       <c r="B28" s="83" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C28" s="90" t="str">
         <f>MAX(C19,C18)*C27</f>
@@ -3495,7 +3492,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="B29" s="83" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C29" s="90" t="str">
         <f>0.16*(MAX(C19,C18)+C28)</f>
@@ -3512,7 +3509,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="B30" s="83" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C30" s="90" t="str">
         <f>0.02*(MAX(C19,C18)+C28)</f>
@@ -3529,7 +3526,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="B31" s="83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C31" s="90" t="str">
         <f>0.035*(MAX(C18,C19) +C28+C29+C30)</f>
@@ -3546,7 +3543,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="B32" s="83" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" s="90" t="str">
         <f>SUM(C28:C31)</f>
@@ -3563,7 +3560,7 @@
     </row>
     <row r="37" spans="1:9">
       <c r="B37" s="84" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C37" s="83"/>
       <c r="D37" s="83"/>
@@ -3571,7 +3568,7 @@
     </row>
     <row r="40" spans="1:9">
       <c r="B40" s="83" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C40" s="90" t="str">
         <f>C13*E40</f>
@@ -3591,21 +3588,21 @@
     </row>
     <row r="43" spans="1:9">
       <c r="B43" s="83" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C43" s="83" t="s">
+        <v>49</v>
+      </c>
+      <c r="D43" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="D43" s="83" t="s">
-        <v>51</v>
-      </c>
       <c r="E43" s="83" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="B44" s="83" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C44" s="90" t="str">
         <f>SUM(C15,C40,C32,(C26))</f>
@@ -3622,7 +3619,7 @@
     </row>
     <row r="45" spans="1:9">
       <c r="B45" s="83" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="83">
         <v>290</v>
@@ -3634,7 +3631,7 @@
     </row>
     <row r="46" spans="1:9">
       <c r="B46" s="83" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C46" s="90" t="str">
         <f>SUM(C44/C45)</f>
@@ -3648,7 +3645,7 @@
     </row>
     <row r="47" spans="1:9">
       <c r="B47" s="83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C47" s="94" t="str">
         <f>C46*3.7</f>

--- a/assets/downloads/CotizacionJIMMY MARCELO HUATUCO.xlsx
+++ b/assets/downloads/CotizacionJIMMY MARCELO HUATUCO.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="118">
   <si>
     <t>PRO MUNDO COMEX S.A.C.</t>
   </si>
@@ -32,7 +32,7 @@
     <t>NOMBRE:</t>
   </si>
   <si>
-    <t>Jimmy Marcelo Huatuco</t>
+    <t>JIMMY MARCELO HUATUCO</t>
   </si>
   <si>
     <t>SERVICIO:</t>
@@ -53,7 +53,7 @@
     <t>PESO:</t>
   </si>
   <si>
-    <t>240.3 Kg</t>
+    <t>234 Kg</t>
   </si>
   <si>
     <t>DNI/RUC:</t>
@@ -71,6 +71,9 @@
     <t>TELEFONO:</t>
   </si>
   <si>
+    <t>946 049 931</t>
+  </si>
+  <si>
     <t>CLIENTE:</t>
   </si>
   <si>
@@ -110,12 +113,12 @@
     <t>ADVALOREM</t>
   </si>
   <si>
-    <t>Hola Jimmy Marcelo Huatuco 😁 un gusto saludarte!
+    <t>Hola JIMMY MARCELO HUATUCO 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
         ☑️Costo CBM: $415.8
-        ☑️Impuestos: $551.81
-        ☑️ Total: $967.61
+        ☑️Impuestos: $644.63
+        ☑️ Total: $1060.43
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -177,7 +180,13 @@
     <t>SET DE PLATO DE SILICONA</t>
   </si>
   <si>
-    <t>INDIVIDUAL DE MESA</t>
+    <t>BABERO DE SILICONA</t>
+  </si>
+  <si>
+    <t>CAMA PARA MASCOTAS DE TIBURON</t>
+  </si>
+  <si>
+    <t>CAMA PARA GATOS DE TIBURON</t>
   </si>
   <si>
     <t>NOTAS:</t>
@@ -518,18 +527,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0"/>
     <numFmt numFmtId="166" formatCode="_-[$$-540A]* #,##0.00_ ;_-[$$-540A]* \-#,##0.00\ ;_-[$$-540A]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.0_ ;_-[$$-409]* \-#,##0.0\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="168" formatCode="_-[$S/-280A]\ * #,##0.00_-;\-[$S/-280A]\ * #,##0.00_-;_-[$S/-280A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.0\ &quot;kg&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.0\ &quot;cm&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0.000\ &quot;m3&quot;"/>
-    <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0.00_-"/>
-    <numFmt numFmtId="173" formatCode="0.00&quot; Kg&quot;"/>
-    <numFmt numFmtId="174" formatCode="&quot;S/.&quot; #,##0.00_-"/>
+    <numFmt numFmtId="167" formatCode="_-[$S/-280A]\ * #,##0.00_-;\-[$S/-280A]\ * #,##0.00_-;_-[$S/-280A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="0.0\ &quot;kg&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0\ &quot;cm&quot;"/>
+    <numFmt numFmtId="170" formatCode="#,##0.000\ &quot;m3&quot;"/>
+    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0.00_-"/>
+    <numFmt numFmtId="172" formatCode="0.00&quot; Kg&quot;"/>
+    <numFmt numFmtId="173" formatCode="&quot;S/.&quot; #,##0.00_-"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -587,15 +595,6 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
       <b val="0"/>
       <i val="0"/>
       <strike val="0"/>
@@ -612,6 +611,15 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri Light"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b val="0"/>
@@ -704,7 +712,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -768,12 +776,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="009999"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -880,7 +882,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="100">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -890,12 +892,6 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="3" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="164" fillId="3" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -929,9 +925,6 @@
     <xf xfId="0" fontId="5" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="2" numFmtId="166" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -956,9 +949,6 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -977,31 +967,28 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="8" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="167" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="166" fillId="3" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="167" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="167" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="167" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="166" fillId="3" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="168" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="168" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="168" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="168" fillId="3" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0">
+    <xf xfId="0" fontId="0" numFmtId="167" fillId="3" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
@@ -1013,7 +1000,7 @@
     <xf xfId="0" fontId="4" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="9" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
@@ -1025,7 +1012,7 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="169" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="168" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -1049,7 +1036,7 @@
     <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="168" fillId="4" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="6" numFmtId="167" fillId="4" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
@@ -1097,7 +1084,7 @@
     <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="170" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="169" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="14" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0">
@@ -1127,7 +1114,7 @@
     <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="171" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="170" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0">
@@ -1142,19 +1129,19 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="9" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="9" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="10" borderId="1" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="7" numFmtId="0" fillId="9" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="9" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="172" fillId="2" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0">
+    <xf xfId="0" fontId="0" numFmtId="171" fillId="2" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="173" fillId="2" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="172" fillId="2" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0">
@@ -1163,31 +1150,28 @@
     <xf xfId="0" fontId="0" numFmtId="10" fillId="2" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="174" fillId="2" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0">
+    <xf xfId="0" fontId="0" numFmtId="173" fillId="2" borderId="1" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="172" fillId="2" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0">
+    <xf xfId="0" fontId="1" numFmtId="171" fillId="2" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="17" numFmtId="10" fillId="2" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="0">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="172" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="18" numFmtId="174" fillId="11" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="168" fillId="4" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="7" numFmtId="168" fillId="12" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="168" fillId="12" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="171" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="18" numFmtId="173" fillId="11" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="167" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="171" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="4" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
@@ -1612,1434 +1596,1473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" customHeight="1" ht="18" s="0" customFormat="1">
-      <c r="A1" s="52"/>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
+      <c r="A1" s="47"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
     </row>
     <row r="2" spans="1:14" customHeight="1" ht="18">
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
     </row>
     <row r="3" spans="1:14" customHeight="1" ht="25.8">
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="E3" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="E3" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
     </row>
     <row r="4" spans="1:14" customHeight="1" ht="25.8">
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="E4" s="64" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="E4" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="15"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="B5" s="47"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="45"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="40"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="47"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
-      <c r="E7" s="49" t="s">
+      <c r="A7" s="42"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="E7" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="44"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="105" t="s">
+      <c r="C8" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="26" t="s">
+      <c r="D8" s="38"/>
+      <c r="E8" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="54" t="s">
+      <c r="F8" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="55"/>
-      <c r="H8" s="42"/>
+      <c r="G8" s="50"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="71" t="str">
+      <c r="J8" s="66" t="str">
         <f>+'2'!F7</f>
         <v>0</v>
       </c>
-      <c r="K8" s="71"/>
-      <c r="L8" s="71"/>
+      <c r="K8" s="66"/>
+      <c r="L8" s="66"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="27" t="s">
+      <c r="C9" s="16"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="50" t="str">
+      <c r="F9" s="45" t="str">
         <f>+TODAY()</f>
         <v>0</v>
       </c>
-      <c r="G9" s="51"/>
-      <c r="H9" s="42"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="104" t="s">
+      <c r="J9" s="98" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="48"/>
-      <c r="L9" s="48"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="16">
         <v>10723807234</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="31" t="s">
+      <c r="D10" s="38"/>
+      <c r="E10" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="52" t="s">
+      <c r="F10" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="53"/>
-      <c r="H10" s="42"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="72"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="72"/>
+      <c r="J10" s="67"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="20">
-        <v>51912705923</v>
-      </c>
-      <c r="D11" s="44"/>
-      <c r="E11" s="28" t="s">
+      <c r="C11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="57" t="s">
+      <c r="D11" s="39"/>
+      <c r="E11" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="74"/>
-      <c r="H11" s="42"/>
+      <c r="F11" s="52" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="69"/>
+      <c r="H11" s="37"/>
       <c r="I11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="103" t="str">
-        <f>'2'!E7</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
+        <v>20</v>
+      </c>
+      <c r="J11" s="97" t="str">
+        <f>'2'!G7</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="B12" s="52"/>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47"/>
+      <c r="L12" s="47"/>
     </row>
     <row r="13" spans="1:14">
-      <c r="B13" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="75"/>
-      <c r="K13" s="12" t="s">
+      <c r="B13" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="10" t="s">
         <v>22</v>
       </c>
+      <c r="L13" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="71"/>
+      <c r="F14" s="71"/>
+      <c r="G14" s="71"/>
+      <c r="H14" s="71"/>
+      <c r="I14" s="71"/>
+      <c r="J14" s="71"/>
+      <c r="K14" s="14" t="str">
+        <f>'2'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15" s="72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="15" t="str">
+        <f>'2'!G14 + '2'!G17</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="14" t="str">
+        <f>SUM(K14:K15)</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="B19" s="73" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="76"/>
-      <c r="E14" s="76"/>
-      <c r="F14" s="76"/>
-      <c r="G14" s="76"/>
-      <c r="H14" s="76"/>
-      <c r="I14" s="76"/>
-      <c r="J14" s="76"/>
-      <c r="K14" s="17" t="str">
-        <f>'2'!E11</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="B15" s="77" t="s">
+    </row>
+    <row r="20" spans="1:14">
+      <c r="B20" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="20" t="str">
+        <f>MAX('2'!C27:F27)</f>
+        <v>0</v>
+      </c>
+      <c r="K20" s="14" t="str">
+        <f>'2'!G28</f>
+        <v>0</v>
+      </c>
+      <c r="L20" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
-      <c r="K15" s="18" t="str">
-        <f>'2'!E14 + '2'!E17</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="B16" s="60" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="17" t="str">
-        <f>SUM(K14:K15)</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="B19" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
-      <c r="J19" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="12" t="s">
+      <c r="N20" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="B21" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53"/>
+      <c r="E21" s="53"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="53"/>
+      <c r="H21" s="53"/>
+      <c r="I21" s="53"/>
+      <c r="J21" s="20">
+        <v>0.16</v>
+      </c>
+      <c r="K21" s="14" t="str">
+        <f>'2'!G29</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="B22" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="K22" s="14" t="str">
+        <f>'2'!G30</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="B23" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="31" t="str">
+        <f>SUM(K20:K22)</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="B25" s="52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="52"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="52"/>
+      <c r="J25" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="K25" s="15" t="str">
+        <f>'2'!G31</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="B26" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="55"/>
+      <c r="H26" s="55"/>
+      <c r="I26" s="55"/>
+      <c r="K26" s="14" t="str">
+        <f>K23+K25</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+    </row>
+    <row r="28" spans="1:14" customHeight="1" ht="15.6">
+      <c r="B28" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="56"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="28" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="B20" s="58" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="23" t="str">
-        <f>MAX('2'!C27:D27)</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="17" t="str">
-        <f>'2'!E28</f>
-        <v>0</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="N20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="B21" s="58" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="23">
-        <v>0.16</v>
-      </c>
-      <c r="K21" s="17" t="str">
-        <f>'2'!E29</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="B22" s="57" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="57"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="23">
-        <v>0.02</v>
-      </c>
-      <c r="K22" s="17" t="str">
-        <f>'2'!E30</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="B23" s="60" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="35"/>
-      <c r="K23" s="36" t="str">
-        <f>SUM(K20:K22)</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="35" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="11"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="B25" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="K25" s="18" t="str">
-        <f>'2'!E31</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="B26" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
-      <c r="E26" s="60"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="60"/>
-      <c r="H26" s="60"/>
-      <c r="I26" s="60"/>
-      <c r="K26" s="17" t="str">
-        <f>K23+K25</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-    </row>
-    <row r="28" spans="1:14" customHeight="1" ht="15.6">
-      <c r="B28" s="61" t="s">
+      <c r="L28" s="28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="B29" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="14" t="str">
+        <f>K14</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="B30" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="14" t="str">
+        <f>IF(J11&lt;1, '2'!K7, '2'!K7*J11)</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="B31" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="15" t="str">
+        <f>K26</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="B32" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="55"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="55"/>
+      <c r="H32" s="55"/>
+      <c r="I32" s="55"/>
+      <c r="J32" s="55"/>
+      <c r="K32" s="14" t="str">
+        <f>SUM(K29:K31)</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="54"/>
+      <c r="H33" s="54"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="54"/>
+      <c r="K33" s="54"/>
+      <c r="L33" s="54"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="B34" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="64"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="64"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="64"/>
+      <c r="K34" s="64"/>
+      <c r="L34" s="65"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="B35" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="61"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G35" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="62"/>
+      <c r="I35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J35" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-      <c r="E28" s="61"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61"/>
-      <c r="J28" s="61"/>
-      <c r="K28" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="L28" s="32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="B29" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="58"/>
-      <c r="K29" s="17" t="str">
-        <f>K14</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="B30" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="58"/>
-      <c r="K30" s="17" t="str">
-        <f>IF(J11&lt;1, '2'!I7, '2'!I7*J11)</f>
-        <v>0</v>
-      </c>
-      <c r="L30" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="B31" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="57"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="18" t="str">
-        <f>K26</f>
-        <v>0</v>
-      </c>
-      <c r="L31" s="14" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="B32" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="17" t="str">
-        <f>SUM(K29:K31)</f>
-        <v>0</v>
-      </c>
-      <c r="L32" s="11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="B33" s="59"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="59"/>
-      <c r="F33" s="59"/>
-      <c r="G33" s="59"/>
-      <c r="H33" s="59"/>
-      <c r="I33" s="59"/>
-      <c r="J33" s="59"/>
-      <c r="K33" s="59"/>
-      <c r="L33" s="59"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="B34" s="68" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="69"/>
-      <c r="K34" s="69"/>
-      <c r="L34" s="70"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="B35" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="65" t="s">
-        <v>44</v>
-      </c>
-      <c r="D35" s="66"/>
-      <c r="E35" s="67"/>
-      <c r="F35" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G35" s="65" t="s">
-        <v>46</v>
-      </c>
-      <c r="H35" s="67"/>
-      <c r="I35" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="J35" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="K35" s="56" t="s">
-        <v>48</v>
-      </c>
-      <c r="L35" s="56"/>
+      <c r="K35" s="51" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="51"/>
     </row>
     <row r="36" spans="1:14">
-      <c r="B36" s="7">
+      <c r="B36" s="5">
         <v>1</v>
       </c>
-      <c r="C36" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7" t="str">
+      <c r="C36" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5" t="str">
         <f>'2'!C10</f>
         <v>0</v>
       </c>
-      <c r="G36" s="97" t="str">
+      <c r="G36" s="92" t="str">
         <f>'2'!C8</f>
         <v>0</v>
       </c>
-      <c r="H36" s="8"/>
-      <c r="I36" s="97" t="str">
+      <c r="H36" s="6"/>
+      <c r="I36" s="92" t="str">
         <f>'2'!C46</f>
         <v>0</v>
       </c>
-      <c r="J36" s="97" t="str">
+      <c r="J36" s="92" t="str">
         <f>'2'!C44</f>
         <v>0</v>
       </c>
-      <c r="K36" s="98" t="str">
+      <c r="K36" s="93" t="str">
         <f>'2'!C47</f>
         <v>0</v>
       </c>
-      <c r="L36" s="56"/>
+      <c r="L36" s="51"/>
       <c r="M36" s="1"/>
     </row>
     <row r="37" spans="1:14">
-      <c r="B37" s="7">
+      <c r="B37" s="5">
         <v>2</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7" t="str">
+      <c r="C37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5" t="str">
         <f>'2'!D10</f>
         <v>0</v>
       </c>
-      <c r="G37" s="97" t="str">
+      <c r="G37" s="92" t="str">
         <f>'2'!D8</f>
         <v>0</v>
       </c>
-      <c r="H37" s="8"/>
-      <c r="I37" s="97" t="str">
+      <c r="H37" s="6"/>
+      <c r="I37" s="92" t="str">
         <f>'2'!D46</f>
         <v>0</v>
       </c>
-      <c r="J37" s="97" t="str">
+      <c r="J37" s="92" t="str">
         <f>'2'!D44</f>
         <v>0</v>
       </c>
-      <c r="K37" s="98" t="str">
+      <c r="K37" s="93" t="str">
         <f>'2'!D47</f>
         <v>0</v>
       </c>
-      <c r="L37" s="56"/>
+      <c r="L37" s="51"/>
       <c r="M37" s="1"/>
     </row>
     <row r="38" spans="1:14">
-      <c r="B38" s="102" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
-      <c r="F38" s="7" t="str">
-        <f>SUM(F36:F37)</f>
-        <v>0</v>
-      </c>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="97" t="str">
-        <f>SUM(J36:J37)</f>
-        <v>0</v>
-      </c>
-      <c r="K38" s="100"/>
-      <c r="L38" s="99"/>
+      <c r="B38" s="5">
+        <v>3</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5" t="str">
+        <f>'2'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="92" t="str">
+        <f>'2'!E8</f>
+        <v>0</v>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="92" t="str">
+        <f>'2'!E46</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="92" t="str">
+        <f>'2'!E44</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="93" t="str">
+        <f>'2'!E47</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="51"/>
       <c r="M38" s="1"/>
     </row>
     <row r="39" spans="1:14" customHeight="1" ht="15.6">
-      <c r="B39" s="25"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="101"/>
-      <c r="L39" s="38"/>
+      <c r="B39" s="5">
+        <v>4</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5" t="str">
+        <f>'2'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="92" t="str">
+        <f>'2'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="H39" s="5"/>
+      <c r="I39" s="92" t="str">
+        <f>'2'!F46</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="92" t="str">
+        <f>'2'!F44</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="93" t="str">
+        <f>'2'!F47</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="94"/>
       <c r="M39" s="1"/>
     </row>
     <row r="40" spans="1:14" customHeight="1" ht="15.6">
-      <c r="B40" s="25"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="16"/>
+      <c r="B40" s="95" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="5" t="str">
+        <f>SUM(F36:F39)</f>
+        <v>0</v>
+      </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="37"/>
-      <c r="L40" s="38"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="96" t="str">
+        <f>SUM(J36:J39)</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="32"/>
+      <c r="L40" s="33"/>
     </row>
     <row r="41" spans="1:14">
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="40"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="35"/>
     </row>
     <row r="42" spans="1:14" customHeight="1" ht="18">
-      <c r="B42" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
+      <c r="B42" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
     </row>
     <row r="43" spans="1:14" customHeight="1" ht="18">
-      <c r="B43" s="73" t="s">
-        <v>52</v>
-      </c>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="73"/>
-      <c r="F43" s="73"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="73"/>
-      <c r="K43" s="73"/>
-      <c r="L43" s="73"/>
+      <c r="B43" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="68"/>
+      <c r="D43" s="68"/>
+      <c r="E43" s="68"/>
+      <c r="F43" s="68"/>
+      <c r="G43" s="68"/>
+      <c r="H43" s="68"/>
+      <c r="I43" s="68"/>
+      <c r="J43" s="68"/>
+      <c r="K43" s="68"/>
+      <c r="L43" s="68"/>
     </row>
     <row r="44" spans="1:14" customHeight="1" ht="18">
-      <c r="B44" s="73" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="73"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="73"/>
-      <c r="F44" s="73"/>
-      <c r="G44" s="73"/>
-      <c r="H44" s="73"/>
-      <c r="I44" s="73"/>
-      <c r="J44" s="73"/>
-      <c r="K44" s="73"/>
-      <c r="L44" s="73"/>
+      <c r="B44" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="C44" s="68"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="68"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="68"/>
+      <c r="J44" s="68"/>
+      <c r="K44" s="68"/>
+      <c r="L44" s="68"/>
     </row>
     <row r="45" spans="1:14" customHeight="1" ht="18">
-      <c r="B45" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="C45" s="73"/>
-      <c r="D45" s="73"/>
-      <c r="E45" s="73"/>
-      <c r="F45" s="73"/>
-      <c r="G45" s="73"/>
-      <c r="H45" s="73"/>
-      <c r="I45" s="73"/>
-      <c r="J45" s="73"/>
-      <c r="K45" s="73"/>
-      <c r="L45" s="73"/>
+      <c r="B45" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="68"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
+      <c r="H45" s="68"/>
+      <c r="I45" s="68"/>
+      <c r="J45" s="68"/>
+      <c r="K45" s="68"/>
+      <c r="L45" s="68"/>
     </row>
     <row r="46" spans="1:14" customHeight="1" ht="18">
-      <c r="B46" s="73" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
-      <c r="G46" s="73"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="73"/>
-      <c r="J46" s="73"/>
-      <c r="K46" s="73"/>
-      <c r="L46" s="73"/>
+      <c r="B46" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="68"/>
+      <c r="J46" s="68"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="68"/>
     </row>
     <row r="47" spans="1:14" customHeight="1" ht="18">
-      <c r="B47" s="73" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" s="73"/>
-      <c r="D47" s="73"/>
-      <c r="E47" s="73"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73"/>
-      <c r="J47" s="73"/>
-      <c r="K47" s="73"/>
-      <c r="L47" s="73"/>
+      <c r="B47" s="68" t="s">
+        <v>59</v>
+      </c>
+      <c r="C47" s="68"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="68"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="68"/>
     </row>
     <row r="48" spans="1:14">
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
+      <c r="J48" s="7"/>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:14" customHeight="1" ht="9">
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="47"/>
-      <c r="K49" s="47"/>
-      <c r="L49" s="47"/>
-      <c r="M49" s="47"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
+      <c r="L49" s="42"/>
+      <c r="M49" s="42"/>
     </row>
     <row r="50" spans="1:14" customHeight="1" ht="31.8">
-      <c r="B50" s="47"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="46"/>
-      <c r="L50" s="46"/>
-      <c r="M50" s="46"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
+      <c r="J50" s="41"/>
+      <c r="K50" s="41"/>
+      <c r="L50" s="41"/>
+      <c r="M50" s="41"/>
     </row>
     <row r="51" spans="1:14" customHeight="1" ht="21">
-      <c r="B51" s="47"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="E51" s="62"/>
-      <c r="F51" s="62"/>
-      <c r="G51" s="62"/>
-      <c r="H51" s="62"/>
-      <c r="I51" s="62"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
     </row>
     <row r="52" spans="1:14">
-      <c r="B52" s="47"/>
-      <c r="C52" s="47"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="42"/>
     </row>
     <row r="53" spans="1:14">
-      <c r="B53" s="47"/>
-      <c r="C53" s="47"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="42"/>
     </row>
     <row r="54" spans="1:14" customHeight="1" ht="21">
-      <c r="B54" s="79" t="s">
-        <v>58</v>
-      </c>
-      <c r="C54" s="79"/>
-      <c r="D54" s="79"/>
-      <c r="E54" s="79"/>
-      <c r="F54" s="79"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="79"/>
-      <c r="I54" s="79"/>
-      <c r="J54" s="79"/>
-      <c r="K54" s="79"/>
-      <c r="L54" s="79"/>
+      <c r="B54" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="74"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74"/>
+      <c r="J54" s="74"/>
+      <c r="K54" s="74"/>
+      <c r="L54" s="74"/>
     </row>
     <row r="56" spans="1:14">
-      <c r="B56" s="80" t="s">
-        <v>59</v>
-      </c>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="80"/>
-      <c r="I56" s="80"/>
-      <c r="J56" s="80"/>
-      <c r="K56" s="80"/>
-      <c r="L56" s="80"/>
+      <c r="B56" s="75" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="75"/>
+      <c r="D56" s="75"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="75"/>
+      <c r="G56" s="75"/>
+      <c r="H56" s="75"/>
+      <c r="I56" s="75"/>
+      <c r="J56" s="75"/>
+      <c r="K56" s="75"/>
+      <c r="L56" s="75"/>
     </row>
     <row r="57" spans="1:14">
-      <c r="B57" s="80" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" s="80"/>
-      <c r="D57" s="80"/>
-      <c r="E57" s="80"/>
-      <c r="F57" s="80"/>
-      <c r="G57" s="80"/>
-      <c r="H57" s="80"/>
-      <c r="I57" s="80"/>
-      <c r="J57" s="80"/>
-      <c r="K57" s="80"/>
-      <c r="L57" s="80"/>
+      <c r="B57" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75"/>
+      <c r="H57" s="75"/>
+      <c r="I57" s="75"/>
+      <c r="J57" s="75"/>
+      <c r="K57" s="75"/>
+      <c r="L57" s="75"/>
     </row>
     <row r="58" spans="1:14">
-      <c r="B58" s="58" t="s">
-        <v>61</v>
-      </c>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="58"/>
-      <c r="F58" s="58"/>
-      <c r="G58" s="58"/>
-      <c r="H58" s="58"/>
-      <c r="I58" s="58"/>
-      <c r="J58" s="58"/>
-      <c r="K58" s="58"/>
-      <c r="L58" s="58"/>
+      <c r="B58" s="53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" s="53"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="53"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="B59" s="80" t="s">
-        <v>62</v>
-      </c>
-      <c r="C59" s="80"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="80"/>
-      <c r="F59" s="80"/>
-      <c r="G59" s="80"/>
-      <c r="H59" s="80"/>
-      <c r="I59" s="80"/>
-      <c r="J59" s="80"/>
-      <c r="K59" s="80"/>
-      <c r="L59" s="80"/>
+      <c r="B59" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="75"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="75"/>
+      <c r="H59" s="75"/>
+      <c r="I59" s="75"/>
+      <c r="J59" s="75"/>
+      <c r="K59" s="75"/>
+      <c r="L59" s="75"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="B60" s="80" t="s">
-        <v>63</v>
-      </c>
-      <c r="C60" s="80"/>
-      <c r="D60" s="80"/>
-      <c r="E60" s="80"/>
-      <c r="F60" s="80"/>
-      <c r="G60" s="80"/>
-      <c r="H60" s="80"/>
-      <c r="I60" s="80"/>
-      <c r="J60" s="80"/>
-      <c r="K60" s="80"/>
-      <c r="L60" s="80"/>
+      <c r="B60" s="75" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" s="75"/>
+      <c r="D60" s="75"/>
+      <c r="E60" s="75"/>
+      <c r="F60" s="75"/>
+      <c r="G60" s="75"/>
+      <c r="H60" s="75"/>
+      <c r="I60" s="75"/>
+      <c r="J60" s="75"/>
+      <c r="K60" s="75"/>
+      <c r="L60" s="75"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="B61" s="58" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="58"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="58"/>
-      <c r="F61" s="58"/>
-      <c r="G61" s="58"/>
-      <c r="H61" s="58"/>
-      <c r="I61" s="58"/>
-      <c r="J61" s="58"/>
-      <c r="K61" s="58"/>
-      <c r="L61" s="58"/>
+      <c r="B61" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" s="53"/>
+      <c r="D61" s="53"/>
+      <c r="E61" s="53"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="53"/>
+      <c r="H61" s="53"/>
+      <c r="I61" s="53"/>
+      <c r="J61" s="53"/>
+      <c r="K61" s="53"/>
+      <c r="L61" s="53"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="B62" s="80" t="s">
-        <v>65</v>
-      </c>
-      <c r="C62" s="80"/>
-      <c r="D62" s="80"/>
-      <c r="E62" s="80"/>
-      <c r="F62" s="80"/>
-      <c r="G62" s="80"/>
-      <c r="H62" s="80"/>
-      <c r="I62" s="80"/>
-      <c r="J62" s="80"/>
-      <c r="K62" s="80"/>
-      <c r="L62" s="80"/>
+      <c r="B62" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="75"/>
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
+      <c r="F62" s="75"/>
+      <c r="G62" s="75"/>
+      <c r="H62" s="75"/>
+      <c r="I62" s="75"/>
+      <c r="J62" s="75"/>
+      <c r="K62" s="75"/>
+      <c r="L62" s="75"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="B63" s="80" t="s">
-        <v>66</v>
-      </c>
-      <c r="C63" s="80"/>
-      <c r="D63" s="80"/>
-      <c r="E63" s="80"/>
-      <c r="F63" s="80"/>
-      <c r="G63" s="80"/>
-      <c r="H63" s="80"/>
-      <c r="I63" s="80"/>
-      <c r="J63" s="80"/>
-      <c r="K63" s="80"/>
-      <c r="L63" s="80"/>
+      <c r="B63" s="75" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="75"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="75"/>
+      <c r="F63" s="75"/>
+      <c r="G63" s="75"/>
+      <c r="H63" s="75"/>
+      <c r="I63" s="75"/>
+      <c r="J63" s="75"/>
+      <c r="K63" s="75"/>
+      <c r="L63" s="75"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="B64" s="80" t="s">
-        <v>67</v>
-      </c>
-      <c r="C64" s="80"/>
-      <c r="D64" s="80"/>
-      <c r="E64" s="80"/>
-      <c r="F64" s="80"/>
-      <c r="G64" s="80"/>
-      <c r="H64" s="80"/>
-      <c r="I64" s="80"/>
-      <c r="J64" s="80"/>
-      <c r="K64" s="80"/>
-      <c r="L64" s="80"/>
+      <c r="B64" s="75" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" s="75"/>
+      <c r="D64" s="75"/>
+      <c r="E64" s="75"/>
+      <c r="F64" s="75"/>
+      <c r="G64" s="75"/>
+      <c r="H64" s="75"/>
+      <c r="I64" s="75"/>
+      <c r="J64" s="75"/>
+      <c r="K64" s="75"/>
+      <c r="L64" s="75"/>
     </row>
     <row r="65" spans="1:14">
-      <c r="B65" s="80" t="s">
-        <v>68</v>
-      </c>
-      <c r="C65" s="80"/>
-      <c r="D65" s="80"/>
-      <c r="E65" s="80"/>
-      <c r="F65" s="80"/>
-      <c r="G65" s="80"/>
-      <c r="H65" s="80"/>
-      <c r="I65" s="80"/>
-      <c r="J65" s="80"/>
-      <c r="K65" s="80"/>
-      <c r="L65" s="80"/>
+      <c r="B65" s="75" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="75"/>
+      <c r="D65" s="75"/>
+      <c r="E65" s="75"/>
+      <c r="F65" s="75"/>
+      <c r="G65" s="75"/>
+      <c r="H65" s="75"/>
+      <c r="I65" s="75"/>
+      <c r="J65" s="75"/>
+      <c r="K65" s="75"/>
+      <c r="L65" s="75"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="B66" s="80" t="s">
-        <v>69</v>
-      </c>
-      <c r="C66" s="80"/>
-      <c r="D66" s="80"/>
-      <c r="E66" s="80"/>
-      <c r="F66" s="80"/>
-      <c r="G66" s="80"/>
-      <c r="H66" s="80"/>
-      <c r="I66" s="80"/>
-      <c r="J66" s="80"/>
-      <c r="K66" s="80"/>
-      <c r="L66" s="80"/>
+      <c r="B66" s="75" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" s="75"/>
+      <c r="D66" s="75"/>
+      <c r="E66" s="75"/>
+      <c r="F66" s="75"/>
+      <c r="G66" s="75"/>
+      <c r="H66" s="75"/>
+      <c r="I66" s="75"/>
+      <c r="J66" s="75"/>
+      <c r="K66" s="75"/>
+      <c r="L66" s="75"/>
     </row>
     <row r="67" spans="1:14">
-      <c r="B67" s="80" t="s">
-        <v>70</v>
-      </c>
-      <c r="C67" s="80"/>
-      <c r="D67" s="80"/>
-      <c r="E67" s="80"/>
-      <c r="F67" s="80"/>
-      <c r="G67" s="80"/>
-      <c r="H67" s="80"/>
-      <c r="I67" s="80"/>
-      <c r="J67" s="80"/>
-      <c r="K67" s="80"/>
-      <c r="L67" s="80"/>
+      <c r="B67" s="75" t="s">
+        <v>73</v>
+      </c>
+      <c r="C67" s="75"/>
+      <c r="D67" s="75"/>
+      <c r="E67" s="75"/>
+      <c r="F67" s="75"/>
+      <c r="G67" s="75"/>
+      <c r="H67" s="75"/>
+      <c r="I67" s="75"/>
+      <c r="J67" s="75"/>
+      <c r="K67" s="75"/>
+      <c r="L67" s="75"/>
     </row>
     <row r="68" spans="1:14">
-      <c r="B68" s="80" t="s">
-        <v>71</v>
-      </c>
-      <c r="C68" s="80"/>
-      <c r="D68" s="80"/>
-      <c r="E68" s="80"/>
-      <c r="F68" s="80"/>
-      <c r="G68" s="80"/>
-      <c r="H68" s="80"/>
-      <c r="I68" s="80"/>
-      <c r="J68" s="80"/>
-      <c r="K68" s="80"/>
-      <c r="L68" s="80"/>
+      <c r="B68" s="75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" s="75"/>
+      <c r="D68" s="75"/>
+      <c r="E68" s="75"/>
+      <c r="F68" s="75"/>
+      <c r="G68" s="75"/>
+      <c r="H68" s="75"/>
+      <c r="I68" s="75"/>
+      <c r="J68" s="75"/>
+      <c r="K68" s="75"/>
+      <c r="L68" s="75"/>
     </row>
     <row r="69" spans="1:14">
-      <c r="B69" s="80" t="s">
-        <v>72</v>
-      </c>
-      <c r="C69" s="80"/>
-      <c r="D69" s="80"/>
-      <c r="E69" s="80"/>
-      <c r="F69" s="80"/>
-      <c r="G69" s="80"/>
-      <c r="H69" s="80"/>
-      <c r="I69" s="80"/>
-      <c r="J69" s="80"/>
-      <c r="K69" s="80"/>
-      <c r="L69" s="80"/>
+      <c r="B69" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" s="75"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="75"/>
+      <c r="F69" s="75"/>
+      <c r="G69" s="75"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="75"/>
+      <c r="J69" s="75"/>
+      <c r="K69" s="75"/>
+      <c r="L69" s="75"/>
     </row>
     <row r="70" spans="1:14">
-      <c r="B70" s="80" t="s">
-        <v>73</v>
-      </c>
-      <c r="C70" s="80"/>
-      <c r="D70" s="80"/>
-      <c r="E70" s="80"/>
-      <c r="F70" s="80"/>
-      <c r="G70" s="80"/>
-      <c r="H70" s="80"/>
-      <c r="I70" s="80"/>
-      <c r="J70" s="80"/>
-      <c r="K70" s="80"/>
-      <c r="L70" s="80"/>
+      <c r="B70" s="75" t="s">
+        <v>76</v>
+      </c>
+      <c r="C70" s="75"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="75"/>
+      <c r="F70" s="75"/>
+      <c r="G70" s="75"/>
+      <c r="H70" s="75"/>
+      <c r="I70" s="75"/>
+      <c r="J70" s="75"/>
+      <c r="K70" s="75"/>
+      <c r="L70" s="75"/>
     </row>
     <row r="71" spans="1:14">
-      <c r="B71" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="C71" s="80"/>
-      <c r="D71" s="80"/>
-      <c r="E71" s="80"/>
-      <c r="F71" s="80"/>
-      <c r="G71" s="80"/>
-      <c r="H71" s="80"/>
-      <c r="I71" s="80"/>
-      <c r="J71" s="80"/>
-      <c r="K71" s="80"/>
-      <c r="L71" s="80"/>
+      <c r="B71" s="75" t="s">
+        <v>77</v>
+      </c>
+      <c r="C71" s="75"/>
+      <c r="D71" s="75"/>
+      <c r="E71" s="75"/>
+      <c r="F71" s="75"/>
+      <c r="G71" s="75"/>
+      <c r="H71" s="75"/>
+      <c r="I71" s="75"/>
+      <c r="J71" s="75"/>
+      <c r="K71" s="75"/>
+      <c r="L71" s="75"/>
     </row>
     <row r="72" spans="1:14">
-      <c r="B72" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="C72" s="80"/>
-      <c r="D72" s="80"/>
-      <c r="E72" s="80"/>
-      <c r="F72" s="80"/>
-      <c r="G72" s="80"/>
-      <c r="H72" s="80"/>
-      <c r="I72" s="80"/>
-      <c r="J72" s="80"/>
-      <c r="K72" s="80"/>
-      <c r="L72" s="80"/>
+      <c r="B72" s="75" t="s">
+        <v>78</v>
+      </c>
+      <c r="C72" s="75"/>
+      <c r="D72" s="75"/>
+      <c r="E72" s="75"/>
+      <c r="F72" s="75"/>
+      <c r="G72" s="75"/>
+      <c r="H72" s="75"/>
+      <c r="I72" s="75"/>
+      <c r="J72" s="75"/>
+      <c r="K72" s="75"/>
+      <c r="L72" s="75"/>
     </row>
     <row r="73" spans="1:14">
-      <c r="B73" s="76" t="s">
-        <v>76</v>
-      </c>
-      <c r="C73" s="76"/>
-      <c r="D73" s="76"/>
-      <c r="E73" s="76"/>
-      <c r="F73" s="76"/>
-      <c r="G73" s="76"/>
-      <c r="H73" s="76"/>
-      <c r="I73" s="76"/>
-      <c r="J73" s="76"/>
-      <c r="K73" s="76"/>
-      <c r="L73" s="76"/>
+      <c r="B73" s="71" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" s="71"/>
+      <c r="D73" s="71"/>
+      <c r="E73" s="71"/>
+      <c r="F73" s="71"/>
+      <c r="G73" s="71"/>
+      <c r="H73" s="71"/>
+      <c r="I73" s="71"/>
+      <c r="J73" s="71"/>
+      <c r="K73" s="71"/>
+      <c r="L73" s="71"/>
     </row>
     <row r="74" spans="1:14">
-      <c r="B74" s="80" t="s">
-        <v>77</v>
-      </c>
-      <c r="C74" s="80"/>
-      <c r="D74" s="80"/>
-      <c r="E74" s="80"/>
-      <c r="F74" s="80"/>
-      <c r="G74" s="80"/>
-      <c r="H74" s="80"/>
-      <c r="I74" s="80"/>
-      <c r="J74" s="80"/>
-      <c r="K74" s="80"/>
-      <c r="L74" s="80"/>
+      <c r="B74" s="75" t="s">
+        <v>80</v>
+      </c>
+      <c r="C74" s="75"/>
+      <c r="D74" s="75"/>
+      <c r="E74" s="75"/>
+      <c r="F74" s="75"/>
+      <c r="G74" s="75"/>
+      <c r="H74" s="75"/>
+      <c r="I74" s="75"/>
+      <c r="J74" s="75"/>
+      <c r="K74" s="75"/>
+      <c r="L74" s="75"/>
     </row>
     <row r="75" spans="1:14">
-      <c r="B75" s="76" t="s">
-        <v>78</v>
-      </c>
-      <c r="C75" s="76"/>
-      <c r="D75" s="76"/>
-      <c r="E75" s="76"/>
-      <c r="F75" s="76"/>
-      <c r="G75" s="76"/>
-      <c r="H75" s="76"/>
-      <c r="I75" s="76"/>
-      <c r="J75" s="76"/>
-      <c r="K75" s="76"/>
-      <c r="L75" s="76"/>
+      <c r="B75" s="71" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="71"/>
+      <c r="D75" s="71"/>
+      <c r="E75" s="71"/>
+      <c r="F75" s="71"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="71"/>
+      <c r="I75" s="71"/>
+      <c r="J75" s="71"/>
+      <c r="K75" s="71"/>
+      <c r="L75" s="71"/>
     </row>
     <row r="76" spans="1:14">
-      <c r="B76" s="80" t="s">
-        <v>79</v>
-      </c>
-      <c r="C76" s="80"/>
-      <c r="D76" s="80"/>
-      <c r="E76" s="80"/>
-      <c r="F76" s="80"/>
-      <c r="G76" s="80"/>
-      <c r="H76" s="80"/>
-      <c r="I76" s="80"/>
-      <c r="J76" s="80"/>
-      <c r="K76" s="80"/>
-      <c r="L76" s="80"/>
+      <c r="B76" s="75" t="s">
+        <v>82</v>
+      </c>
+      <c r="C76" s="75"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="75"/>
+      <c r="F76" s="75"/>
+      <c r="G76" s="75"/>
+      <c r="H76" s="75"/>
+      <c r="I76" s="75"/>
+      <c r="J76" s="75"/>
+      <c r="K76" s="75"/>
+      <c r="L76" s="75"/>
     </row>
     <row r="77" spans="1:14">
-      <c r="B77" s="80" t="s">
-        <v>80</v>
-      </c>
-      <c r="C77" s="80"/>
-      <c r="D77" s="80"/>
-      <c r="E77" s="80"/>
-      <c r="F77" s="80"/>
-      <c r="G77" s="80"/>
-      <c r="H77" s="80"/>
-      <c r="I77" s="80"/>
-      <c r="J77" s="80"/>
-      <c r="K77" s="80"/>
-      <c r="L77" s="80"/>
+      <c r="B77" s="75" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" s="75"/>
+      <c r="D77" s="75"/>
+      <c r="E77" s="75"/>
+      <c r="F77" s="75"/>
+      <c r="G77" s="75"/>
+      <c r="H77" s="75"/>
+      <c r="I77" s="75"/>
+      <c r="J77" s="75"/>
+      <c r="K77" s="75"/>
+      <c r="L77" s="75"/>
     </row>
     <row r="78" spans="1:14">
-      <c r="B78" s="80" t="s">
-        <v>81</v>
-      </c>
-      <c r="C78" s="80"/>
-      <c r="D78" s="80"/>
-      <c r="E78" s="80"/>
-      <c r="F78" s="80"/>
-      <c r="G78" s="80"/>
-      <c r="H78" s="80"/>
-      <c r="I78" s="80"/>
-      <c r="J78" s="80"/>
-      <c r="K78" s="80"/>
-      <c r="L78" s="80"/>
+      <c r="B78" s="75" t="s">
+        <v>84</v>
+      </c>
+      <c r="C78" s="75"/>
+      <c r="D78" s="75"/>
+      <c r="E78" s="75"/>
+      <c r="F78" s="75"/>
+      <c r="G78" s="75"/>
+      <c r="H78" s="75"/>
+      <c r="I78" s="75"/>
+      <c r="J78" s="75"/>
+      <c r="K78" s="75"/>
+      <c r="L78" s="75"/>
     </row>
     <row r="79" spans="1:14">
-      <c r="B79" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="C79" s="80"/>
-      <c r="D79" s="80"/>
-      <c r="E79" s="80"/>
-      <c r="F79" s="80"/>
-      <c r="G79" s="80"/>
-      <c r="H79" s="80"/>
-      <c r="I79" s="80"/>
-      <c r="J79" s="80"/>
-      <c r="K79" s="80"/>
-      <c r="L79" s="80"/>
+      <c r="B79" s="75" t="s">
+        <v>85</v>
+      </c>
+      <c r="C79" s="75"/>
+      <c r="D79" s="75"/>
+      <c r="E79" s="75"/>
+      <c r="F79" s="75"/>
+      <c r="G79" s="75"/>
+      <c r="H79" s="75"/>
+      <c r="I79" s="75"/>
+      <c r="J79" s="75"/>
+      <c r="K79" s="75"/>
+      <c r="L79" s="75"/>
     </row>
     <row r="80" spans="1:14">
-      <c r="B80" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="C80" s="80"/>
-      <c r="D80" s="80"/>
-      <c r="E80" s="80"/>
-      <c r="F80" s="80"/>
-      <c r="G80" s="80"/>
-      <c r="H80" s="80"/>
-      <c r="I80" s="80"/>
-      <c r="J80" s="80"/>
-      <c r="K80" s="80"/>
-      <c r="L80" s="80"/>
+      <c r="B80" s="75" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" s="75"/>
+      <c r="D80" s="75"/>
+      <c r="E80" s="75"/>
+      <c r="F80" s="75"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="75"/>
+      <c r="I80" s="75"/>
+      <c r="J80" s="75"/>
+      <c r="K80" s="75"/>
+      <c r="L80" s="75"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="41"/>
-      <c r="B81" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="C81" s="81"/>
-      <c r="D81" s="81"/>
-      <c r="E81" s="81"/>
-      <c r="F81" s="81"/>
-      <c r="G81" s="81"/>
-      <c r="H81" s="81"/>
-      <c r="I81" s="81"/>
-      <c r="J81" s="81"/>
-      <c r="K81" s="81"/>
-      <c r="L81" s="81"/>
+      <c r="A81" s="36"/>
+      <c r="B81" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="C81" s="76"/>
+      <c r="D81" s="76"/>
+      <c r="E81" s="76"/>
+      <c r="F81" s="76"/>
+      <c r="G81" s="76"/>
+      <c r="H81" s="76"/>
+      <c r="I81" s="76"/>
+      <c r="J81" s="76"/>
+      <c r="K81" s="76"/>
+      <c r="L81" s="76"/>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="41"/>
-      <c r="B82" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="C82" s="80"/>
-      <c r="D82" s="80"/>
-      <c r="E82" s="80"/>
-      <c r="F82" s="80"/>
-      <c r="G82" s="80"/>
-      <c r="H82" s="80"/>
-      <c r="I82" s="80"/>
-      <c r="J82" s="80"/>
-      <c r="K82" s="80"/>
-      <c r="L82" s="80"/>
+      <c r="A82" s="36"/>
+      <c r="B82" s="75" t="s">
+        <v>88</v>
+      </c>
+      <c r="C82" s="75"/>
+      <c r="D82" s="75"/>
+      <c r="E82" s="75"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="75"/>
+      <c r="I82" s="75"/>
+      <c r="J82" s="75"/>
+      <c r="K82" s="75"/>
+      <c r="L82" s="75"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="41"/>
-      <c r="B83" s="81" t="s">
-        <v>86</v>
-      </c>
-      <c r="C83" s="81"/>
-      <c r="D83" s="81"/>
-      <c r="E83" s="81"/>
-      <c r="F83" s="81"/>
-      <c r="G83" s="81"/>
-      <c r="H83" s="81"/>
-      <c r="I83" s="81"/>
-      <c r="J83" s="81"/>
-      <c r="K83" s="81"/>
-      <c r="L83" s="81"/>
+      <c r="A83" s="36"/>
+      <c r="B83" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="C83" s="76"/>
+      <c r="D83" s="76"/>
+      <c r="E83" s="76"/>
+      <c r="F83" s="76"/>
+      <c r="G83" s="76"/>
+      <c r="H83" s="76"/>
+      <c r="I83" s="76"/>
+      <c r="J83" s="76"/>
+      <c r="K83" s="76"/>
+      <c r="L83" s="76"/>
     </row>
     <row r="85" spans="1:14">
-      <c r="C85" s="47"/>
-      <c r="D85" s="47"/>
-      <c r="E85" s="47"/>
-      <c r="F85" s="47"/>
-      <c r="G85" s="47"/>
-      <c r="H85" s="47"/>
-      <c r="I85" s="47"/>
+      <c r="C85" s="42"/>
+      <c r="D85" s="42"/>
+      <c r="E85" s="42"/>
+      <c r="F85" s="42"/>
+      <c r="G85" s="42"/>
+      <c r="H85" s="42"/>
+      <c r="I85" s="42"/>
     </row>
     <row r="86" spans="1:14">
-      <c r="C86" s="47"/>
-      <c r="D86" s="47"/>
-      <c r="E86" s="47"/>
-      <c r="F86" s="47"/>
-      <c r="G86" s="47"/>
-      <c r="H86" s="47"/>
-      <c r="I86" s="47"/>
+      <c r="C86" s="42"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="42"/>
     </row>
     <row r="87" spans="1:14">
-      <c r="C87" s="47"/>
-      <c r="D87" s="47"/>
-      <c r="E87" s="47"/>
-      <c r="F87" s="47"/>
-      <c r="G87" s="47"/>
-      <c r="H87" s="47"/>
-      <c r="I87" s="47"/>
+      <c r="C87" s="42"/>
+      <c r="D87" s="42"/>
+      <c r="E87" s="42"/>
+      <c r="F87" s="42"/>
+      <c r="G87" s="42"/>
+      <c r="H87" s="42"/>
+      <c r="I87" s="42"/>
     </row>
     <row r="88" spans="1:14">
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
+      <c r="C88" s="42"/>
+      <c r="D88" s="42"/>
+      <c r="E88" s="42"/>
+      <c r="F88" s="42"/>
+      <c r="G88" s="42"/>
+      <c r="H88" s="42"/>
+      <c r="I88" s="42"/>
     </row>
     <row r="89" spans="1:14">
-      <c r="C89" s="47"/>
-      <c r="D89" s="47"/>
-      <c r="E89" s="47"/>
-      <c r="F89" s="47"/>
-      <c r="G89" s="47"/>
-      <c r="H89" s="47"/>
-      <c r="I89" s="47"/>
+      <c r="C89" s="42"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+      <c r="G89" s="42"/>
+      <c r="H89" s="42"/>
+      <c r="I89" s="42"/>
     </row>
     <row r="90" spans="1:14">
-      <c r="C90" s="47"/>
-      <c r="D90" s="47"/>
-      <c r="E90" s="47"/>
-      <c r="F90" s="47"/>
-      <c r="G90" s="47"/>
-      <c r="H90" s="47"/>
-      <c r="I90" s="47"/>
+      <c r="C90" s="42"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
+      <c r="G90" s="42"/>
+      <c r="H90" s="42"/>
+      <c r="I90" s="42"/>
     </row>
     <row r="91" spans="1:14">
-      <c r="C91" s="47"/>
-      <c r="D91" s="47"/>
-      <c r="E91" s="47"/>
-      <c r="F91" s="47"/>
-      <c r="G91" s="47"/>
-      <c r="H91" s="47"/>
-      <c r="I91" s="47"/>
+      <c r="C91" s="42"/>
+      <c r="D91" s="42"/>
+      <c r="E91" s="42"/>
+      <c r="F91" s="42"/>
+      <c r="G91" s="42"/>
+      <c r="H91" s="42"/>
+      <c r="I91" s="42"/>
     </row>
     <row r="92" spans="1:14" customHeight="1" ht="15.6">
-      <c r="C92" s="47"/>
-      <c r="D92" s="47"/>
-      <c r="E92" s="47"/>
-      <c r="F92" s="47"/>
-      <c r="G92" s="47"/>
-      <c r="H92" s="47"/>
-      <c r="I92" s="47"/>
+      <c r="C92" s="42"/>
+      <c r="D92" s="42"/>
+      <c r="E92" s="42"/>
+      <c r="F92" s="42"/>
+      <c r="G92" s="42"/>
+      <c r="H92" s="42"/>
+      <c r="I92" s="42"/>
     </row>
     <row r="93" spans="1:14" customHeight="1" ht="15.6">
-      <c r="C93" s="47"/>
-      <c r="D93" s="47"/>
-      <c r="E93" s="47"/>
-      <c r="F93" s="47"/>
-      <c r="G93" s="47"/>
-      <c r="H93" s="47"/>
-      <c r="I93" s="47"/>
+      <c r="C93" s="42"/>
+      <c r="D93" s="42"/>
+      <c r="E93" s="42"/>
+      <c r="F93" s="42"/>
+      <c r="G93" s="42"/>
+      <c r="H93" s="42"/>
+      <c r="I93" s="42"/>
     </row>
     <row r="94" spans="1:14">
-      <c r="C94" s="47"/>
-      <c r="D94" s="47"/>
-      <c r="E94" s="47"/>
-      <c r="F94" s="47"/>
-      <c r="G94" s="47"/>
-      <c r="H94" s="47"/>
-      <c r="I94" s="47"/>
+      <c r="C94" s="42"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="42"/>
+      <c r="F94" s="42"/>
+      <c r="G94" s="42"/>
+      <c r="H94" s="42"/>
+      <c r="I94" s="42"/>
     </row>
     <row r="100" spans="1:14" customHeight="1" ht="15.6"/>
   </sheetData>
@@ -3051,6 +3074,7 @@
     <mergeCell ref="I7:L7"/>
     <mergeCell ref="B58:L58"/>
     <mergeCell ref="B47:L47"/>
+    <mergeCell ref="C38:E38"/>
     <mergeCell ref="K38:L38"/>
     <mergeCell ref="B43:L43"/>
     <mergeCell ref="B56:L56"/>
@@ -3133,7 +3157,9 @@
     <mergeCell ref="B28:J28"/>
     <mergeCell ref="B29:J29"/>
     <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="K39:L39"/>
     <mergeCell ref="C8:C9"/>
   </mergeCells>
   <dataValidations count="5">
@@ -3176,486 +3202,692 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="2" max="2" width="24.708252" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="29.421387" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="22.280273" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="12.854004" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="35.2771" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="31.706543" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="12.854004" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:9">
-      <c r="B3" s="84" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="B5" s="87" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="89" t="s">
-        <v>49</v>
-      </c>
-      <c r="D5" s="89" t="s">
+    <row r="3" spans="1:11">
+      <c r="B3" s="79" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="89" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="83" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="83">
-        <v>0</v>
-      </c>
-      <c r="D6" s="83">
-        <v>0</v>
-      </c>
-      <c r="E6" s="91">
-        <v>240.3</v>
-      </c>
-      <c r="H6" s="85" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="85" t="s">
+      <c r="D5" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="84" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="84" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="84" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="B7" s="83" t="s">
+    <row r="6" spans="1:11">
+      <c r="B6" s="78" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="83">
-        <v>0</v>
-      </c>
-      <c r="D7" s="83">
-        <v>0</v>
-      </c>
-      <c r="E7" s="92">
-        <v>1.02</v>
-      </c>
-      <c r="H7" s="86" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="86">
+      <c r="C6" s="78">
+        <v>0</v>
+      </c>
+      <c r="D6" s="78">
+        <v>0</v>
+      </c>
+      <c r="E6" s="78">
+        <v>0</v>
+      </c>
+      <c r="F6" s="78">
+        <v>0</v>
+      </c>
+      <c r="G6" s="86">
+        <v>234</v>
+      </c>
+      <c r="J6" s="80" t="s">
+        <v>94</v>
+      </c>
+      <c r="K6" s="80" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="78" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="78">
+        <v>0</v>
+      </c>
+      <c r="D7" s="78">
+        <v>0</v>
+      </c>
+      <c r="E7" s="78">
+        <v>0</v>
+      </c>
+      <c r="F7" s="78">
+        <v>0</v>
+      </c>
+      <c r="G7" s="87">
+        <v>1.73</v>
+      </c>
+      <c r="J7" s="81" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="81">
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="B8" s="83" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="90">
-        <v>7.5283251231527</v>
-      </c>
-      <c r="D8" s="90">
-        <v>1.5357142857143</v>
-      </c>
-      <c r="E8" s="83"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="B9" s="88" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="90">
-        <v>0</v>
-      </c>
-      <c r="D9" s="90">
-        <v>0</v>
-      </c>
-      <c r="E9" s="83"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10" s="83" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="83">
-        <v>290</v>
-      </c>
-      <c r="D10" s="83">
-        <v>30</v>
-      </c>
-      <c r="E10" s="83" t="str">
-        <f>SUM(C10:D10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="B11" s="83" t="s">
+    <row r="8" spans="1:11">
+      <c r="B8" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="90" t="str">
+      <c r="C8" s="85">
+        <v>5.5571428571429</v>
+      </c>
+      <c r="D8" s="85">
+        <v>1.4181818181818</v>
+      </c>
+      <c r="E8" s="85">
+        <v>4.965</v>
+      </c>
+      <c r="F8" s="85">
+        <v>5.3673469387755</v>
+      </c>
+      <c r="G8" s="78"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="83" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="85">
+        <v>0</v>
+      </c>
+      <c r="D9" s="85">
+        <v>0</v>
+      </c>
+      <c r="E9" s="85">
+        <v>0</v>
+      </c>
+      <c r="F9" s="85">
+        <v>0</v>
+      </c>
+      <c r="G9" s="78"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" s="78" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="78">
+        <v>300</v>
+      </c>
+      <c r="D10" s="78">
+        <v>165</v>
+      </c>
+      <c r="E10" s="78">
+        <v>60</v>
+      </c>
+      <c r="F10" s="78">
+        <v>56</v>
+      </c>
+      <c r="G10" s="78" t="str">
+        <f>SUM(C10:F10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="78" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="85" t="str">
         <f>C8*C10</f>
         <v>0</v>
       </c>
-      <c r="D11" s="90" t="str">
+      <c r="D11" s="85" t="str">
         <f>D8*D10</f>
         <v>0</v>
       </c>
-      <c r="E11" s="95" t="str">
-        <f>SUM(C11:D11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="B12" s="88" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="90" t="str">
+      <c r="E11" s="85" t="str">
+        <f>E8*E10</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="85" t="str">
+        <f>F8*F10</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="90" t="str">
+        <f>SUM(C11:F11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="B12" s="83" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="85" t="str">
         <f>C10*C9</f>
         <v>0</v>
       </c>
-      <c r="D12" s="90" t="str">
+      <c r="D12" s="85" t="str">
         <f>D10*D9</f>
         <v>0</v>
       </c>
-      <c r="E12" s="95" t="str">
-        <f>SUM(C12:D12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="B13" s="83" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="93" t="str">
-        <f>C11/E11</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="93" t="str">
-        <f>D11/E11</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="83"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="B14" s="83" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="90" t="str">
-        <f>E14*C13</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="90" t="str">
-        <f>E14*D13</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="95" t="str">
-        <f>IF(E7&lt;1, I7*0.6, I7*0.6*E7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="B15" s="83" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="90" t="str">
+      <c r="E12" s="85" t="str">
+        <f>E10*E9</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="85" t="str">
+        <f>F10*F9</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="90" t="str">
+        <f>SUM(C12:F12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" s="78" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="88" t="str">
+        <f>C11/G11</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="88" t="str">
+        <f>D11/G11</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="88" t="str">
+        <f>E11/G11</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="88" t="str">
+        <f>F11/G11</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="78"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" s="78" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="85" t="str">
+        <f>G14*C13</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="85" t="str">
+        <f>G14*D13</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="85" t="str">
+        <f>G14*E13</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="85" t="str">
+        <f>G14*F13</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="90" t="str">
+        <f>IF(G7&lt;1, K7*0.6, K7*0.6*G7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" s="78" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="85" t="str">
         <f>C11+C14</f>
         <v>0</v>
       </c>
-      <c r="D15" s="90" t="str">
+      <c r="D15" s="85" t="str">
         <f>D11+D14</f>
         <v>0</v>
       </c>
-      <c r="E15" s="95" t="str">
-        <f>SUM(C15:D15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="B16" s="88" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="90" t="str">
+      <c r="E15" s="85" t="str">
+        <f>E11+E14</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="85" t="str">
+        <f>F11+F14</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="90" t="str">
+        <f>SUM(C15:F15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="83" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="85" t="str">
         <f>C12+C14</f>
         <v>0</v>
       </c>
-      <c r="D16" s="90" t="str">
+      <c r="D16" s="85" t="str">
         <f>D12+D14</f>
         <v>0</v>
       </c>
-      <c r="E16" s="95" t="str">
-        <f>SUM(C16:D16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="B17" s="83" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="90" t="str">
-        <f>IF(E15&gt;5000,100*C13,50*C13)</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="90" t="str">
-        <f>IF(E15&gt;5000,100*D13,50*D13)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="95" t="str">
-        <f>SUM(C17:D17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="B18" s="83" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="90" t="str">
+      <c r="E16" s="85" t="str">
+        <f>E12+E14</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="85" t="str">
+        <f>F12+F14</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="90" t="str">
+        <f>SUM(C16:F16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="B17" s="78" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="85" t="str">
+        <f>IF(G15&gt;5000,100*C13,50*C13)</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="85" t="str">
+        <f>IF(G15&gt;5000,100*D13,50*D13)</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="85" t="str">
+        <f>IF(G15&gt;5000,100*E13,50*E13)</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="85" t="str">
+        <f>IF(G15&gt;5000,100*F13,50*F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="90" t="str">
+        <f>SUM(C17:F17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="B18" s="78" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="85" t="str">
         <f>C15+C17</f>
         <v>0</v>
       </c>
-      <c r="D18" s="90" t="str">
+      <c r="D18" s="85" t="str">
         <f>D15+D17</f>
         <v>0</v>
       </c>
-      <c r="E18" s="95" t="str">
-        <f>SUM(C18:D18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="B19" s="88" t="s">
-        <v>105</v>
-      </c>
-      <c r="C19" s="90" t="str">
+      <c r="E18" s="85" t="str">
+        <f>E15+E17</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="85" t="str">
+        <f>F15+F17</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="90" t="str">
+        <f>SUM(C18:F18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="B19" s="83" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="85" t="str">
         <f>C16+C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="90" t="str">
+      <c r="D19" s="85" t="str">
         <f>D16+D17</f>
         <v>0</v>
       </c>
-      <c r="E19" s="95" t="str">
-        <f>SUM(C19:D19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="B23" s="84" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="B26" s="83" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" s="90">
-        <v>0</v>
-      </c>
-      <c r="D26" s="90">
-        <v>0</v>
-      </c>
-      <c r="E26" s="90" t="str">
-        <f>SUM(C26:D26)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="C27" s="96">
-        <v>0</v>
-      </c>
-      <c r="D27" s="96">
-        <v>0</v>
-      </c>
-      <c r="E27" s="93" t="str">
-        <f>SUM(C27:D27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="B28" s="83" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="90" t="str">
+      <c r="E19" s="85" t="str">
+        <f>E16+E17</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="85" t="str">
+        <f>F16+F17</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="90" t="str">
+        <f>SUM(C19:F19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="B23" s="79" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="B26" s="78" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="85">
+        <v>0</v>
+      </c>
+      <c r="D26" s="85">
+        <v>0</v>
+      </c>
+      <c r="E26" s="85">
+        <v>0</v>
+      </c>
+      <c r="F26" s="85">
+        <v>0</v>
+      </c>
+      <c r="G26" s="85" t="str">
+        <f>SUM(C26:F26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="C27" s="91">
+        <v>0</v>
+      </c>
+      <c r="D27" s="91">
+        <v>0</v>
+      </c>
+      <c r="E27" s="91">
+        <v>0</v>
+      </c>
+      <c r="F27" s="91">
+        <v>0</v>
+      </c>
+      <c r="G27" s="88" t="str">
+        <f>SUM(C27:F27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="B28" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="85" t="str">
         <f>MAX(C19,C18)*C27</f>
         <v>0</v>
       </c>
-      <c r="D28" s="90" t="str">
+      <c r="D28" s="85" t="str">
         <f>MAX(D19,D18)*D27</f>
         <v>0</v>
       </c>
-      <c r="E28" s="90" t="str">
-        <f>SUM(C28:D28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="B29" s="83" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="90" t="str">
+      <c r="E28" s="85" t="str">
+        <f>MAX(E19,E18)*E27</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="85" t="str">
+        <f>MAX(F19,F18)*F27</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="85" t="str">
+        <f>SUM(C28:F28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="B29" s="78" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="85" t="str">
         <f>0.16*(MAX(C19,C18)+C28)</f>
         <v>0</v>
       </c>
-      <c r="D29" s="90" t="str">
+      <c r="D29" s="85" t="str">
         <f>0.16*(MAX(D19,D18)+D28)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="90" t="str">
-        <f>SUM(C29:D29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="B30" s="83" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="90" t="str">
+      <c r="E29" s="85" t="str">
+        <f>0.16*(MAX(E19,E18)+E28)</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="85" t="str">
+        <f>0.16*(MAX(F19,F18)+F28)</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="85" t="str">
+        <f>SUM(C29:F29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="B30" s="78" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="85" t="str">
         <f>0.02*(MAX(C19,C18)+C28)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="90" t="str">
+      <c r="D30" s="85" t="str">
         <f>0.02*(MAX(D19,D18)+D28)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="90" t="str">
-        <f>SUM(C30:D30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="B31" s="83" t="s">
-        <v>109</v>
-      </c>
-      <c r="C31" s="90" t="str">
+      <c r="E30" s="85" t="str">
+        <f>0.02*(MAX(E19,E18)+E28)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="85" t="str">
+        <f>0.02*(MAX(F19,F18)+F28)</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="85" t="str">
+        <f>SUM(C30:F30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="B31" s="78" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" s="85" t="str">
         <f>0.035*(MAX(C18,C19) +C28+C29+C30)</f>
         <v>0</v>
       </c>
-      <c r="D31" s="90" t="str">
+      <c r="D31" s="85" t="str">
         <f>0.035*(MAX(D18,D19) +D28+D29+D30)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="90" t="str">
-        <f>SUM(C31:D31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="B32" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="90" t="str">
+      <c r="E31" s="85" t="str">
+        <f>0.035*(MAX(E18,E19) +E28+E29+E30)</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="85" t="str">
+        <f>0.035*(MAX(F18,F19) +F28+F29+F30)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="85" t="str">
+        <f>SUM(C31:F31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="B32" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="85" t="str">
         <f>SUM(C28:C31)</f>
         <v>0</v>
       </c>
-      <c r="D32" s="90" t="str">
+      <c r="D32" s="85" t="str">
         <f>SUM(D28:D31)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="90" t="str">
+      <c r="E32" s="85" t="str">
         <f>SUM(E28:E31)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="B37" s="84" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="B40" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="C40" s="90" t="str">
-        <f>C13*E40</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="90" t="str">
-        <f>D13*E40</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="90" t="str">
-        <f>IF(E7&lt;1, I7*0.4,I7*0.4*E7)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+      <c r="F32" s="85" t="str">
+        <f>SUM(F28:F31)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="85" t="str">
+        <f>SUM(G28:G31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="B37" s="79" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="78"/>
+      <c r="D37" s="78"/>
+      <c r="E37" s="78"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="B40" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="85" t="str">
+        <f>C13*G40</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="85" t="str">
+        <f>D13*G40</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="85" t="str">
+        <f>E13*G40</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="85" t="str">
+        <f>F13*G40</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="85" t="str">
+        <f>IF(G7&lt;1, K7*0.4,K7*0.4*G7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="B41"/>
     </row>
-    <row r="43" spans="1:9">
-      <c r="B43" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="D43" s="83" t="s">
+    <row r="43" spans="1:11">
+      <c r="B43" s="78" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="78" t="s">
         <v>50</v>
       </c>
-      <c r="E43" s="83" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="B44" s="83" t="s">
-        <v>112</v>
-      </c>
-      <c r="C44" s="90" t="str">
+      <c r="D43" s="78" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="78" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="78" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="78" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="B44" s="78" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="85" t="str">
         <f>SUM(C15,C40,C32,(C26))</f>
         <v>0</v>
       </c>
-      <c r="D44" s="90" t="str">
+      <c r="D44" s="85" t="str">
         <f>SUM(D15,D40,D32,(D26))</f>
         <v>0</v>
       </c>
-      <c r="E44" s="90" t="str">
-        <f>SUM(C44:D44)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="B45" s="83" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="83">
-        <v>290</v>
-      </c>
-      <c r="D45" s="83">
-        <v>30</v>
-      </c>
-      <c r="E45" s="83"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="B46" s="83" t="s">
-        <v>113</v>
-      </c>
-      <c r="C46" s="90" t="str">
+      <c r="E44" s="85" t="str">
+        <f>SUM(E15,E40,E32,(E26))</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="85" t="str">
+        <f>SUM(F15,F40,F32,(F26))</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="85" t="str">
+        <f>SUM(C44:F44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="B45" s="78" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="78">
+        <v>300</v>
+      </c>
+      <c r="D45" s="78">
+        <v>165</v>
+      </c>
+      <c r="E45" s="78">
+        <v>60</v>
+      </c>
+      <c r="F45" s="78">
+        <v>56</v>
+      </c>
+      <c r="G45" s="78"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="B46" s="78" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" s="85" t="str">
         <f>SUM(C44/C45)</f>
         <v>0</v>
       </c>
-      <c r="D46" s="90" t="str">
+      <c r="D46" s="85" t="str">
         <f>SUM(D44/D45)</f>
         <v>0</v>
       </c>
-      <c r="E46" s="83"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="B47" s="83" t="s">
-        <v>114</v>
-      </c>
-      <c r="C47" s="94" t="str">
+      <c r="E46" s="85" t="str">
+        <f>SUM(E44/E45)</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="85" t="str">
+        <f>SUM(F44/F45)</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="78"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="B47" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="89" t="str">
         <f>C46*3.7</f>
         <v>0</v>
       </c>
-      <c r="D47" s="94" t="str">
+      <c r="D47" s="89" t="str">
         <f>D46*3.7</f>
         <v>0</v>
       </c>
-      <c r="E47" s="83"/>
+      <c r="E47" s="89" t="str">
+        <f>E46*3.7</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="89" t="str">
+        <f>F46*3.7</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="78"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
